--- a/backend/sample_data/06_Dual_Threshold_Failing_Marks_EdgeCase.xlsx
+++ b/backend/sample_data/06_Dual_Threshold_Failing_Marks_EdgeCase.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,11 +449,21 @@
           <t>external_score</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>semester</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>academic_year</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SU2026-0018</t>
+          <t>SU2026-0010</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -466,12 +476,20 @@
       </c>
       <c r="D2" t="n">
         <v>58</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SU2026-0018</t>
+          <t>SU2026-0010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -484,12 +502,20 @@
       </c>
       <c r="D3" t="n">
         <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SU2026-0018</t>
+          <t>SU2026-0010</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -502,12 +528,20 @@
       </c>
       <c r="D4" t="n">
         <v>28</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SU2026-0019</t>
+          <t>SU2026-0014</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -520,6 +554,14 @@
       </c>
       <c r="D5" t="n">
         <v>67.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
   </sheetData>
